--- a/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-visa_pcb3_large.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-visa_pcb3_large.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="padim" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stfpm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="uflow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,105 +478,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -589,116 +580,107 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>41.00636792182922</v>
+        <v>42.46772766113281</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9800000190734864</v>
+        <v>0.959999978542328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1848886758089065</v>
+        <v>0.1884086430072784</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7258687019348145</v>
+        <v>0.7126436829566956</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6757678985595703</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6666666865348816</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3555216491222381</v>
+        <v>0.1715199798345565</v>
       </c>
       <c r="J2" t="n">
-        <v>0.075777567923069</v>
+        <v>0.008863810085340901</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06775319576263419</v>
+        <v>0.0576898672094392</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0150582426618383</v>
+        <v>0.0469253162048744</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08240115227390871</v>
+        <v>5.344877481460571</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0754372484450711</v>
+        <v>34.78698992729187</v>
       </c>
       <c r="O2" t="n">
-        <v>9.080120325088499</v>
-      </c>
-      <c r="P2" t="n">
-        <v>49.68789482116699</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>45.48866081237793</v>
+        <v>28.29596567153931</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-171026</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-162249</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>large</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -710,116 +692,107 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>40.81470608711243</v>
+        <v>42.2986478805542</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9800000190734864</v>
+        <v>0.959999978542328</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1854102164506912</v>
+        <v>0.1862079948186874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.732758641242981</v>
+        <v>0.701195240020752</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6978417038917542</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6844106316566467</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3568983078002929</v>
+        <v>0.1789288371801376</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0772177577018737</v>
+        <v>0.0088984863477362</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06783980131149291</v>
+        <v>0.0577957918790244</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0153843403653323</v>
+        <v>0.0467424206868135</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0837898424411096</v>
+        <v>5.365787267684937</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0752175411774744</v>
+        <v>34.85086250305176</v>
       </c>
       <c r="O3" t="n">
-        <v>9.27675724029541</v>
-      </c>
-      <c r="P3" t="n">
-        <v>50.52527499198914</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>45.35617733001709</v>
+        <v>28.18567967414856</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-171331</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-162554</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>large</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -831,116 +804,107 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>41.14477300643921</v>
+        <v>42.01349663734436</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9300000071525574</v>
+        <v>0.9800000190734864</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1851035058498382</v>
+        <v>0.1845590323209762</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7333333492279053</v>
+        <v>0.7419354915618896</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6901408433914185</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6711864471435547</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3557771444320678</v>
+        <v>0.1726758778095245</v>
       </c>
       <c r="J4" t="n">
-        <v>0.074115514755249</v>
+        <v>0.0087538560231526</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06859733909368509</v>
+        <v>0.0575065600931347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0154908245080343</v>
+        <v>0.0469080101000531</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0806706149384354</v>
+        <v>5.27857518196106</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07581070801907309</v>
+        <v>34.67645573616028</v>
       </c>
       <c r="O4" t="n">
-        <v>9.340967178344728</v>
-      </c>
-      <c r="P4" t="n">
-        <v>48.64438080787659</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>45.7138569355011</v>
+        <v>28.28553009033203</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-171635</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-162900</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>large</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -952,116 +916,107 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>41.03971290588379</v>
+        <v>42.49558448791504</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9800000190734864</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1846081167459488</v>
+        <v>0.1890820413827896</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7196652889251709</v>
+        <v>0.7264150977134705</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7017543911933899</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7021276354789734</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3552162945270538</v>
+        <v>0.1691811084747314</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0768614634871482</v>
+        <v>0.0089143726165417</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0681654885411262</v>
+        <v>0.0579284257556668</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0157598962831259</v>
+        <v>0.0468682333406919</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0832810322839031</v>
+        <v>5.375366687774658</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0749299498537484</v>
+        <v>34.93084073066711</v>
       </c>
       <c r="O5" t="n">
-        <v>9.503217458724976</v>
-      </c>
-      <c r="P5" t="n">
-        <v>50.2184624671936</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>45.1827597618103</v>
+        <v>28.26154470443726</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-171939</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-163206</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>large</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1073,116 +1028,107 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>41.12423014640808</v>
+        <v>42.21805644035339</v>
       </c>
       <c r="D6" t="n">
         <v>0.9800000190734864</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1850516498088836</v>
+        <v>0.1860546171665191</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7511312365531921</v>
+        <v>0.7464115023612976</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7226277589797974</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.682758629322052</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3557734489440918</v>
+        <v>0.1762271523475647</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0772974044084549</v>
+        <v>0.008905485890200199</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06865740567445749</v>
+        <v>0.0579710330931503</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0150652694860303</v>
+        <v>0.0475638758879198</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0840931286661581</v>
+        <v>5.370007991790772</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07609632596447689</v>
+        <v>34.95653295516968</v>
       </c>
       <c r="O6" t="n">
-        <v>9.084357500076294</v>
-      </c>
-      <c r="P6" t="n">
-        <v>50.70815658569336</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>45.88608455657959</v>
+        <v>28.68101716041565</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-172243</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-163512</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>large</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,105 +1194,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -1357,119 +1293,110 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>155.5440602302551</v>
+        <v>404.6239726543427</v>
       </c>
       <c r="D2" t="n">
-        <v>1.759999990463257</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1834034532308578</v>
+        <v>0.1951253382222992</v>
       </c>
       <c r="F2" t="n">
-        <v>0.813725471496582</v>
+        <v>0.8585366010665894</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6734007000923157</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6644518375396729</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1521794646978378</v>
+        <v>0.1643832176923751</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0725290700793266</v>
+        <v>0.0086009917567618</v>
       </c>
       <c r="K2" t="n">
-        <v>0.064324751496315</v>
+        <v>0.0493930872795396</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008524773330435401</v>
+        <v>0.0405597168810134</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0788491736992477</v>
+        <v>5.186398029327393</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0713860435074636</v>
+        <v>29.78403162956237</v>
       </c>
       <c r="O2" t="n">
-        <v>5.140438318252564</v>
-      </c>
-      <c r="P2" t="n">
-        <v>47.54605174064636</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>43.04578423500061</v>
+        <v>24.4575092792511</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250716-015532</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-175447</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>large</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1478,119 +1405,110 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>155.9245555400848</v>
+        <v>395.5728645324707</v>
       </c>
       <c r="D3" t="n">
-        <v>1.740000009536743</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1817716360092162</v>
+        <v>0.1890040401901517</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8125</v>
+        <v>0.8600000143051147</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6756756901741028</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6644518375396729</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1557104885578155</v>
+        <v>0.1759244799613952</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0699741020798683</v>
+        <v>0.008668173209549299</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0651424974203109</v>
+        <v>0.048822465820692</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0086700390425092</v>
+        <v>0.0402977514029735</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0760049926700876</v>
+        <v>5.226908445358276</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07228747529176929</v>
+        <v>29.43994688987732</v>
       </c>
       <c r="O3" t="n">
-        <v>5.228033542633057</v>
-      </c>
-      <c r="P3" t="n">
-        <v>45.83101058006287</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>43.58934760093689</v>
+        <v>24.29954409599304</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250716-020428</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-175937</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>large</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1599,119 +1517,110 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>155.3215572834015</v>
+        <v>328.3926222324371</v>
       </c>
       <c r="D4" t="n">
-        <v>1.740000009536743</v>
+        <v>1.669999957084656</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1817422300577163</v>
+        <v>0.1979256719350814</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8020304441452026</v>
+        <v>0.8279569745063782</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6688963174819946</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6644518375396729</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1631401479244232</v>
+        <v>0.1713608056306839</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0711565762758255</v>
+        <v>0.0086467922425784</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0649156644940376</v>
+        <v>0.04965297855548</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008785502432195299</v>
+        <v>0.0410258694865414</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07712496453849831</v>
+        <v>5.21401572227478</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0716900999470927</v>
+        <v>29.94074606895447</v>
       </c>
       <c r="O4" t="n">
-        <v>5.29765796661377</v>
-      </c>
-      <c r="P4" t="n">
-        <v>46.50635361671448</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>43.22913026809693</v>
+        <v>24.73859930038452</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250716-021315</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-180427</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>large</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1720,119 +1629,110 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>153.8067538738251</v>
+        <v>344.6252987384796</v>
       </c>
       <c r="D5" t="n">
-        <v>1.759999990463257</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1803075164556503</v>
+        <v>0.1914962468047936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8186046481132507</v>
+        <v>0.7547169923782349</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6688963174819946</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6644518375396729</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1562468409538269</v>
+        <v>0.1714573949575424</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07137081027030941</v>
+        <v>0.008710544896165301</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0653688833117485</v>
+        <v>0.0498937081737107</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0088004287004866</v>
+        <v>0.0404662773581484</v>
       </c>
       <c r="M5" t="n">
-        <v>0.077200890378177</v>
+        <v>5.252458572387695</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0724552855958195</v>
+        <v>30.08590602874756</v>
       </c>
       <c r="O5" t="n">
-        <v>5.306658506393433</v>
-      </c>
-      <c r="P5" t="n">
-        <v>46.55213689804077</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>43.69053721427917</v>
+        <v>24.4011652469635</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250716-022014</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-180917</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>large</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1841,119 +1741,826 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>155.0338010787964</v>
+        <v>272.3758656978607</v>
       </c>
       <c r="D6" t="n">
-        <v>1.759999990463257</v>
+        <v>1.559999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1825459688901901</v>
+        <v>0.1977836555904812</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8358209133148193</v>
+        <v>0.8469387888908386</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6779661178588867</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6644518375396729</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1605558842420578</v>
+        <v>0.1673460155725479</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0715641304850578</v>
+        <v>0.0088315587336348</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0636231675744056</v>
+        <v>0.0496695148411081</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0088445037158567</v>
+        <v>0.0408280401878293</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0776230158102057</v>
+        <v>5.325429916381836</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0703196913053345</v>
+        <v>29.95071744918823</v>
       </c>
       <c r="O6" t="n">
-        <v>5.333235740661621</v>
-      </c>
-      <c r="P6" t="n">
-        <v>46.80667853355408</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>42.4027738571167</v>
+        <v>24.61930823326111</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250716-022729</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-181405</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>visa_pcb3_large</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>training:epoch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>training:e2e_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>training:gpu_mem</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>training:train/iter_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>data_group</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>otx_version</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>otx_ref</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>test_branch</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>test_commit</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_info</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>accelerator_info</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>machine_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>7523.327941417694</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.510000228881836</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2250467647409918</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.801980197429657</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2849642932415008</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0134888604703431</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0796281188281614</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.07027300317489089</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8.133782863616943</v>
+      </c>
+      <c r="N2" t="n">
+        <v>48.01575565338135</v>
+      </c>
+      <c r="O2" t="n">
+        <v>42.37462091445923</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250715-112907</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>visa_pcb3_large</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>199</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7435.458248853683</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.429999828338623</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2211785905025712</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.286733478307724</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0131617082687555</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.08052127159650049</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0728094435449856</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.93651008605957</v>
+      </c>
+      <c r="N3" t="n">
+        <v>48.55432677268982</v>
+      </c>
+      <c r="O3" t="n">
+        <v>43.90409445762634</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250715-133728</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>visa_pcb3_large</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>199</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7412.303404331207</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.429999828338623</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2205390248017095</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7964601516723633</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2683290541172027</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0129877200371788</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.07922951775799141</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0696197690853036</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.831595182418823</v>
+      </c>
+      <c r="N4" t="n">
+        <v>47.77539920806885</v>
+      </c>
+      <c r="O4" t="n">
+        <v>41.98072075843811</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250715-154341</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>visa_pcb3_large</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>199</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7321.484668016434</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.429999828338623</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2160894559256395</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7963801026344299</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2889454960823059</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0137552867085977</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0804995284547062</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0716645697851481</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8.294437885284424</v>
+      </c>
+      <c r="N5" t="n">
+        <v>48.54121565818787</v>
+      </c>
+      <c r="O5" t="n">
+        <v>43.21373558044434</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250715-175010</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>visa_pcb3_large</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>199</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7534.267069578171</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2270490693387074</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8061224222183228</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2490966916084289</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0116992012580631</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.07968810818483971</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0704741655890621</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.054618358612061</v>
+      </c>
+      <c r="N6" t="n">
+        <v>48.05192923545837</v>
+      </c>
+      <c r="O6" t="n">
+        <v>42.49592185020447</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250715-195449</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>visa_pcb3_large</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>visa_pcb3_large</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
